--- a/artfynd/A 4538-2023 artfynd.xlsx
+++ b/artfynd/A 4538-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4538-2023 artfynd.xlsx
+++ b/artfynd/A 4538-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110031344</v>
+        <v>110031345</v>
       </c>
       <c r="B2" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571878.7596869186</v>
+        <v>571827</v>
       </c>
       <c r="R2" t="n">
-        <v>6300245.77703617</v>
+        <v>6300258</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-05-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111782517</v>
+        <v>110031344</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,51 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granhult, Sm</t>
+          <t>Trakten kring Ebbegärde, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571908</v>
+        <v>571879</v>
       </c>
       <c r="R3" t="n">
-        <v>6300255</v>
+        <v>6300246</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,21 +851,133 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111782517</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Granhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>571908</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6300255</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Håkan Lundkvist</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Håkan Lundkvist</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4538-2023 artfynd.xlsx
+++ b/artfynd/A 4538-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110031345</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110031344</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,8 +993,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111782517</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>